--- a/docs/02_기능정의서.xlsx
+++ b/docs/02_기능정의서.xlsx
@@ -88,7 +88,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -110,11 +110,55 @@
         <color rgb="00CFE3F0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CFE3F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CFE3F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CFE3F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CFE3F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -137,6 +181,8 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -502,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -530,6 +576,9 @@
           <t>기능정의서 (시스템 관점)</t>
         </is>
       </c>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="9" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -539,9 +588,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1</t>
-        </is>
-      </c>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -554,6 +606,9 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -566,6 +621,9 @@
           <t>✅ 완료 / 🔧 진행중 / ⬜ 예정</t>
         </is>
       </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="9" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1104,6 +1162,87 @@
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>프론트 Vercel(자동배포), 백엔드 Oracle VM(systemd)+Caddy 자동 HTTPS, push 시 갱신</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>F-AUTH-05</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>비밀번호 재설정</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-02</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>POST /auth/forgot(재설정 메일 — 계정 존재여부 비노출) → 메일 링크 GET /auth/reset 폼 → POST /auth/reset(토큰 1시간 만료·1회용, bcrypt 갱신)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>F-AUTH-06</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>회원 탈퇴</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-01</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>DELETE /auth/account — 비밀번호 재확인 후 users+user_data 영구 삭제(트랜잭션). 설정 페이지에 경고+비밀번호 확인 단계 UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>F-AUTH-07</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>추천 API 보호</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-01</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>/api/outfit·/api/shop에 JWT 검증 + 계정별 일일 상한(outfit 50/shop 600, lib/auth.js) — 비용 어뷰징 차단</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1285,85 +1424,85 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>/api/state</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>계정 데이터 {settings,closet,favorites}</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>/auth/forgot</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>비밀번호 재설정 메일 요청(존재여부 비노출, 항상 ok)</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>필요</t>
+          <t>불필요</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>/api/settings</t>
+          <t>/auth/reset</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>설정 저장</t>
+          <t>재설정 폼 페이지(메일 링크, 토큰 검사)</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>필요</t>
+          <t>불필요</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>/api/closet</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>옷장 저장</t>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>/auth/reset</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>새 비밀번호 저장(토큰 1시간·1회용)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>필요</t>
+          <t>불필요</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>/api/favorites</t>
+          <t>/auth/account</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>찜 저장</t>
+          <t>회원 탈퇴(비밀번호 재확인, 계정+데이터 삭제)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1380,12 +1519,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>/api/weather</t>
+          <t>/api/state</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>날씨 프록시(nx,ny) {temp,feel,desc,rain,tmx,tmn,pop,reh}</t>
+          <t>계정 데이터 {settings,closet,favorites}</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1397,76 +1536,164 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/api/settings</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>헬스체크</t>
+          <t>설정 저장</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>불필요</t>
+          <t>필요</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>[추천 — Vercel 함수]</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>/api/closet</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>옷장 저장</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>필요</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>/api/shop</t>
+          <t>/api/favorites</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>네이버 쇼핑검색 프록시(query,display)</t>
+          <t>찜 저장</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>불필요</t>
+          <t>필요</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>/api/weather</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>날씨 프록시(nx,ny) {temp,feel,desc,rain,tmx,tmn,pop,reh}</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>/health</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>헬스체크</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>불필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[추천 — Vercel 함수]</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>/api/shop</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>네이버 쇼핑검색 프록시(query,display)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>필요(JWT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>/api/outfit</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>AI 코디 설계(날씨·상황·취향·옷장 → 3세트)</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>불필요</t>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>필요(JWT)</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1534,6 +1761,23 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>F-AUTH-05~07 추가(비밀번호 재설정·회원 탈퇴·추천 API 보호), API 4건 추가, /api/shop·/api/outfit 인증 표기 정정</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">

--- a/docs/02_기능정의서.xlsx
+++ b/docs/02_기능정의서.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -588,7 +588,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="C3" s="8" t="n"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>아이템별 색을 12팔레트로 받아 색칩(스와치+이름) 표시, 옷장과 팔레트 공유</t>
+          <t>아이템별 색을 18팔레트로 받아 색칩(스와치+이름) 표시, 옷장과 팔레트 공유</t>
         </is>
       </c>
     </row>
@@ -1243,6 +1243,60 @@
       <c r="E28" s="5" t="inlineStr">
         <is>
           <t>/api/outfit·/api/shop에 JWT 검증 + 계정별 일일 상한(outfit 50/shop 600, lib/auth.js) — 비용 어뷰징 차단</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>F-CL-03</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>사진 옷 등록</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>REQ-CL-03</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>POST /api/vision — Claude 비전이 사진에서 카테고리·색(18팔레트 enum)·종류를 추출(구조화 출력). 여러 장 병렬 분석 → 한 장씩 확인·수정 후 저장. 사진은 클라이언트에서 1024px 축소, JWT+일일 60회</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>F-PERF-02</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>1세트 우선 로딩</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>REQ-PERF-02</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>/api/outfit에 count·exclude 추가 — 1세트 먼저 생성·즉시 표시 후 나머지 2세트 이어붙임(컨셉 중복 제외). 첫 코디 ~10초→~3초</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1692,6 +1746,28 @@
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>필요(JWT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>/api/vision</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>옷 사진 분석(base64 → 카테고리·색·종류)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>필요(JWT)</t>
         </is>
@@ -1712,7 +1788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1778,6 +1854,23 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>F-CL-03(사진 옷 등록)·F-PERF-02(1세트 우선 로딩) 추가, 색상 칩 18팔레트 반영, API 목록에 /api/vision 추가</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">

--- a/docs/02_기능정의서.xlsx
+++ b/docs/02_기능정의서.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>v4</t>
         </is>
       </c>
       <c r="C3" s="8" t="n"/>
@@ -756,7 +756,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>POST /api/outfit. Claude Haiku가 컨셉·이유·팁·검색어·색·보유옷 포함 3세트 설계. 룰 기반 폴백(TEMP_RANGE+24절기)</t>
+          <t>POST /api/outfit. Claude Haiku가 컨셉·이유·팁·검색어·색·보유옷 포함 3세트 설계. 룰 기반 폴백(TEMP_RANGE+24절기). 상황별 복장 규칙 — 운동이면 운동복·운동화만(룰 폴백 포함), 출근·데이트에 트레이닝복 금지</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1871,6 +1871,23 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>F-OUT-01에 상황별 복장 규칙 추가(운동=운동복·운동화 강제, 룰 폴백 포함)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">

--- a/docs/02_기능정의서.xlsx
+++ b/docs/02_기능정의서.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v4</t>
+          <t>v5</t>
         </is>
       </c>
       <c r="C3" s="8" t="n"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>POST /auth/signup·/auth/login. bcryptjs 해시, JWT 30일. 가입 시 비밀번호 확인·이름(프론트 필수)</t>
+          <t>POST /auth/signup·/auth/login. bcryptjs 해시, JWT 30일. 가입은 인증코드 확인을 마친 이메일만 → verified 계정 생성·즉시 토큰(자동 로그인)</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>가입 시 인증메일(Gmail SMTP) 발송→자동 로그인 X. GET /auth/verify(토큰), 미인증 로그인 403, /auth/resend 재전송</t>
+          <t>가입 전 인증코드(6자리·10분 유효·5회 제한, 메모리 보관) — POST /auth/send-code(중복 확인+메일 발송) → /auth/verify-code(확인). 레거시 미인증 계정용 링크 인증(/auth/verify)·재전송(/auth/resend)·미인증 로그인 403 유지</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>/auth/signup</t>
+          <t>/auth/send-code</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>회원가입 → 인증메일 발송({message})</t>
+          <t>가입 인증코드 메일 발송(중복이면 409)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1390,19 +1390,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>/auth/login</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>로그인 → 토큰(미인증 403)</t>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>/auth/verify-code</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>인증코드 확인(10분·5회 제한)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>/auth/resend</t>
+          <t>/auth/signup</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>인증 메일 재전송</t>
+          <t>회원가입(인증코드 확인 필수) → 즉시 토큰</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1436,17 +1436,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>/auth/verify</t>
+          <t>/auth/login</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>이메일 인증(토큰) → 안내 페이지</t>
+          <t>로그인 → 토큰(미인증 403)</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1458,39 +1458,39 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>/auth/resend</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>인증 메일 재전송 (레거시)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>불필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>/auth/me</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>토큰 검증 → {email,name}</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>/auth/forgot</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>비밀번호 재설정 메일 요청(존재여부 비노출, 항상 ok)</t>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>/auth/verify</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>이메일 인증(토큰) → 안내 페이지 (레거시)</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1507,17 +1507,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>/auth/reset</t>
+          <t>/auth/me</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>재설정 폼 페이지(메일 링크, 토큰 검사)</t>
+          <t>토큰 검증 → {email,name}</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>불필요</t>
+          <t>필요</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>/auth/reset</t>
+          <t>/auth/forgot</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>새 비밀번호 저장(토큰 1시간·1회용)</t>
+          <t>비밀번호 재설정 메일 요청(존재여부 비노출, 항상 ok)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1546,61 +1546,61 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>/auth/account</t>
+          <t>/auth/reset</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>회원 탈퇴(비밀번호 재확인, 계정+데이터 삭제)</t>
+          <t>재설정 폼 페이지(메일 링크, 토큰 검사)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>필요</t>
+          <t>불필요</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>/api/state</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>계정 데이터 {settings,closet,favorites}</t>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>/auth/reset</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>새 비밀번호 저장(토큰 1시간·1회용)</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>필요</t>
+          <t>불필요</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>/api/settings</t>
+          <t>/auth/account</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>설정 저장</t>
+          <t>회원 탈퇴(비밀번호 재확인, 계정+데이터 삭제)</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1612,17 +1612,17 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>/api/closet</t>
+          <t>/api/state</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>옷장 저장</t>
+          <t>계정 데이터 {settings,closet,favorites}</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>/api/favorites</t>
+          <t>/api/settings</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>찜 저장</t>
+          <t>설정 저장</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1656,17 +1656,17 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>/api/weather</t>
+          <t>/api/closet</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>날씨 프록시(nx,ny) {temp,feel,desc,rain,tmx,tmn,pop,reh}</t>
+          <t>옷장 저장</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1678,34 +1678,46 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/api/favorites</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>헬스체크</t>
+          <t>찜 저장</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>불필요</t>
+          <t>필요</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>[추천 — Vercel 함수]</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>/api/weather</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>날씨 프록시(nx,ny) {temp,feel,desc,rain,tmx,tmn,pop,reh}</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>필요</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -1715,59 +1727,91 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>/api/shop</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>네이버 쇼핑검색 프록시(query,display)</t>
+          <t>헬스체크</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>필요(JWT)</t>
+          <t>불필요</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>[추천 — Vercel 함수]</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>/api/shop</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>네이버 쇼핑검색 프록시(query,display)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>필요(JWT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>/api/outfit</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>AI 코디 설계(날씨·상황·취향·옷장 → 3세트)</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>필요(JWT)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>/api/vision</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>옷 사진 분석(base64 → 카테고리·색·종류)</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>필요(JWT)</t>
         </is>
@@ -1788,7 +1832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1888,6 +1932,23 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>v5</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>F-AUTH-01/02 갱신 — 가입 전 인증코드 방식(send-code/verify-code), 가입 즉시 로그인. API 목록 반영</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">

--- a/docs/02_기능정의서.xlsx
+++ b/docs/02_기능정의서.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v5</t>
+          <t>v6</t>
         </is>
       </c>
       <c r="C3" s="8" t="n"/>
@@ -729,7 +729,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>실패 시 localStorage 마지막 날씨(stale) 표시 + '다시 시도', 캐시 없으면 기온 직접 선택 픽커</t>
+          <t>서버: 기상청 실패 시 격자별 마지막 성공 데이터를 stale+asOf로 제공(502 최소화). 프론트: stale이면 "○분 전 날씨" 표시+다시 시도, 서버까지 실패 시 기기 캐시 → 기온 직접 선택 픽커</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>격자(nx,ny)·발표슬롯별 30분 서버 캐시 → 기상청 호출 한도 절감, 키 비노출</t>
+          <t>격자(nx,ny)·발표슬롯별 30분 서버 캐시 + 마지막 성공 데이터 무기한 보관(JSON 파일 영속화, 재시작 유지) + 일시 오류(순간 429·타임아웃) 1.5초 후 1회 재시도 → 기상청 호출 절감·키 비노출·간헐 장애 흡수</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1949,6 +1949,23 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>v6</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>F-WX-03/04 갱신 — 날씨 서버 stale-while-revalidate(마지막 성공 데이터 영속 보관·제공) + 일시 오류 1회 재시도</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">
